--- a/Config/HeroAttribute.xlsx
+++ b/Config/HeroAttribute.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E0BB58-7DFC-4F86-8DCA-1A7C3DE722D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10011758-C30E-4F88-8394-43E184371B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-2910" windowWidth="43200" windowHeight="23055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21600" yWindow="-945" windowWidth="21810" windowHeight="35145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="D5">
         <v>50</v>
@@ -557,7 +557,7 @@
         <v>50</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>50</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>0</v>
